--- a/public/aruba_hotel_history.xlsx
+++ b/public/aruba_hotel_history.xlsx
@@ -483,7 +483,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -520,7 +520,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -557,7 +557,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -594,7 +594,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -631,7 +631,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -668,7 +668,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -705,7 +705,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -742,7 +742,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -779,7 +779,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -816,7 +816,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -853,7 +853,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -890,7 +890,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -927,7 +927,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -964,7 +964,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1073,7 +1073,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1108,7 +1108,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">

--- a/public/aruba_hotel_history.xlsx
+++ b/public/aruba_hotel_history.xlsx
@@ -483,7 +483,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -520,7 +520,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -557,7 +557,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -594,7 +594,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -631,7 +631,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -668,7 +668,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -705,7 +705,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -742,7 +742,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -779,7 +779,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -816,7 +816,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -853,7 +853,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -890,7 +890,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -927,7 +927,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -964,7 +964,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1073,7 +1073,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1108,7 +1108,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">

--- a/public/aruba_hotel_history.xlsx
+++ b/public/aruba_hotel_history.xlsx
@@ -483,7 +483,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -513,14 +513,14 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>https://tourismanalytics.com/uploads/1/2/0/4/120443739/ahata-july-2026_orig.png</t>
+          <t>https://tourismanalytics.weebly.com/uploads/1/2/0/4/120443739/ahata-july-2026_orig.png</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -550,14 +550,14 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>https://tourismanalytics.com/uploads/1/2/0/4/120443739/ahata-july-2026_orig.png</t>
+          <t>https://tourismanalytics.weebly.com/uploads/1/2/0/4/120443739/ahata-july-2026_orig.png</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -587,14 +587,14 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>https://tourismanalytics.com/uploads/1/2/0/4/120443739/ahata-july-2026_orig.png</t>
+          <t>https://tourismanalytics.weebly.com/uploads/1/2/0/4/120443739/ahata-july-2026_orig.png</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -624,14 +624,14 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>https://tourismanalytics.com/uploads/1/2/0/4/120443739/ahata-july-2026_orig.png</t>
+          <t>https://tourismanalytics.weebly.com/uploads/1/2/0/4/120443739/ahata-july-2026_orig.png</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -661,14 +661,14 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>https://tourismanalytics.com/uploads/1/2/0/4/120443739/ahata-july-2026_orig.png</t>
+          <t>https://tourismanalytics.weebly.com/uploads/1/2/0/4/120443739/ahata-july-2026_orig.png</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -698,14 +698,14 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>https://tourismanalytics.com/uploads/1/2/0/4/120443739/ahata-july-2026_orig.png</t>
+          <t>https://tourismanalytics.weebly.com/uploads/1/2/0/4/120443739/ahata-july-2026_orig.png</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -735,14 +735,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>https://tourismanalytics.com/uploads/1/2/0/4/120443739/ahata-july-2026_orig.png</t>
+          <t>https://tourismanalytics.weebly.com/uploads/1/2/0/4/120443739/ahata-july-2026_orig.png</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -772,14 +772,14 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>https://tourismanalytics.com/uploads/1/2/0/4/120443739/ahata-july-2026_orig.png</t>
+          <t>https://tourismanalytics.weebly.com/uploads/1/2/0/4/120443739/ahata-july-2026_orig.png</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -809,14 +809,14 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>https://tourismanalytics.com/uploads/1/2/0/4/120443739/ahata-july-2026_orig.png</t>
+          <t>https://tourismanalytics.weebly.com/uploads/1/2/0/4/120443739/ahata-july-2026_orig.png</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -846,14 +846,14 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>https://tourismanalytics.com/uploads/1/2/0/4/120443739/ahata-july-2026_orig.png</t>
+          <t>https://tourismanalytics.weebly.com/uploads/1/2/0/4/120443739/ahata-july-2026_orig.png</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -883,14 +883,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>https://tourismanalytics.com/uploads/1/2/0/4/120443739/ahata-july-2026_orig.png</t>
+          <t>https://tourismanalytics.weebly.com/uploads/1/2/0/4/120443739/ahata-july-2026_orig.png</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -920,14 +920,14 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>https://tourismanalytics.com/uploads/1/2/0/4/120443739/ahata-july-2026_orig.png</t>
+          <t>https://tourismanalytics.weebly.com/uploads/1/2/0/4/120443739/ahata-july-2026_orig.png</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -957,14 +957,14 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>https://tourismanalytics.com/uploads/1/2/0/4/120443739/ahata-july-2026_orig.png</t>
+          <t>https://tourismanalytics.weebly.com/uploads/1/2/0/4/120443739/ahata-july-2026_orig.png</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>https://tourismanalytics.com/uploads/1/2/0/4/120443739/ahata-july-2026_orig.png</t>
+          <t>https://tourismanalytics.weebly.com/uploads/1/2/0/4/120443739/ahata-july-2026_orig.png</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1101,14 +1101,14 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>https://tourismanalytics.com/uploads/1/2/0/4/120443739/ahata-july-2026_orig.png</t>
+          <t>https://tourismanalytics.weebly.com/uploads/1/2/0/4/120443739/ahata-july-2026_orig.png</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>https://tourismanalytics.com/uploads/1/2/0/4/120443739/ahata-july-2026_orig.png</t>
+          <t>https://tourismanalytics.weebly.com/uploads/1/2/0/4/120443739/ahata-july-2026_orig.png</t>
         </is>
       </c>
     </row>

--- a/public/aruba_hotel_history.xlsx
+++ b/public/aruba_hotel_history.xlsx
@@ -483,7 +483,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -520,7 +520,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -557,7 +557,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -594,7 +594,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -631,7 +631,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -668,7 +668,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -705,7 +705,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -742,7 +742,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -779,7 +779,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -816,7 +816,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -853,7 +853,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -890,7 +890,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -927,7 +927,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -964,7 +964,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1073,7 +1073,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1108,7 +1108,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">

--- a/public/aruba_hotel_history.xlsx
+++ b/public/aruba_hotel_history.xlsx
@@ -419,11 +419,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="39" customWidth="1" min="2" max="2"/>
+    <col width="41" customWidth="1" min="2" max="2"/>
     <col width="6" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="7" customWidth="1" min="5" max="5"/>
@@ -483,12 +483,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Aruba Hotel Performance YTD 2026 July</t>
+          <t>Aruba Hotel Performance YTD 2026 August</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -513,19 +513,19 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>https://tourismanalytics.weebly.com/uploads/1/2/0/4/120443739/ahata-july-2026_orig.png</t>
+          <t>https://tourismanalytics.com/uploads/1/2/0/4/120443739/ahata-august-26_orig.png</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Aruba Hotel Performance YTD 2026 July</t>
+          <t>Aruba Hotel Performance YTD 2026 August</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -550,19 +550,19 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>https://tourismanalytics.weebly.com/uploads/1/2/0/4/120443739/ahata-july-2026_orig.png</t>
+          <t>https://tourismanalytics.com/uploads/1/2/0/4/120443739/ahata-august-26_orig.png</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Aruba Hotel Performance YTD 2026 July</t>
+          <t>Aruba Hotel Performance YTD 2026 August</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -587,19 +587,19 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>https://tourismanalytics.weebly.com/uploads/1/2/0/4/120443739/ahata-july-2026_orig.png</t>
+          <t>https://tourismanalytics.com/uploads/1/2/0/4/120443739/ahata-august-26_orig.png</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Aruba Hotel Performance YTD 2026 July</t>
+          <t>Aruba Hotel Performance YTD 2026 August</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -624,19 +624,19 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>https://tourismanalytics.weebly.com/uploads/1/2/0/4/120443739/ahata-july-2026_orig.png</t>
+          <t>https://tourismanalytics.com/uploads/1/2/0/4/120443739/ahata-august-26_orig.png</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Aruba Hotel Performance YTD 2026 July</t>
+          <t>Aruba Hotel Performance YTD 2026 August</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -661,19 +661,19 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>https://tourismanalytics.weebly.com/uploads/1/2/0/4/120443739/ahata-july-2026_orig.png</t>
+          <t>https://tourismanalytics.com/uploads/1/2/0/4/120443739/ahata-august-26_orig.png</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Aruba Hotel Performance YTD 2026 July</t>
+          <t>Aruba Hotel Performance YTD 2026 August</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -698,19 +698,19 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>https://tourismanalytics.weebly.com/uploads/1/2/0/4/120443739/ahata-july-2026_orig.png</t>
+          <t>https://tourismanalytics.com/uploads/1/2/0/4/120443739/ahata-august-26_orig.png</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Aruba Hotel Performance YTD 2026 July</t>
+          <t>Aruba Hotel Performance YTD 2026 August</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -735,266 +735,340 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>https://tourismanalytics.weebly.com/uploads/1/2/0/4/120443739/ahata-july-2026_orig.png</t>
+          <t>https://tourismanalytics.com/uploads/1/2/0/4/120443739/ahata-august-26_orig.png</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Aruba Hotel Performance YTD 2026 July</t>
+          <t>Aruba Hotel Performance YTD 2026 August</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Jan</t>
+          <t>Aug</t>
         </is>
       </c>
       <c r="F9" s="1" t="n">
-        <v>0.8140000000000001</v>
+        <v>0.738</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>519.26</v>
+        <v>368.53</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>422.91</v>
+        <v>271.96</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>https://tourismanalytics.weebly.com/uploads/1/2/0/4/120443739/ahata-july-2026_orig.png</t>
+          <t>https://tourismanalytics.com/uploads/1/2/0/4/120443739/ahata-august-26_orig.png</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Aruba Hotel Performance YTD 2026 July</t>
+          <t>Aruba Hotel Performance YTD 2026 August</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>2026</v>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Feb</t>
+          <t>Jan</t>
         </is>
       </c>
       <c r="F10" s="1" t="n">
-        <v>0.8959999999999999</v>
+        <v>0.8140000000000001</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>542.95</v>
+        <v>519.26</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>486.27</v>
+        <v>422.91</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>https://tourismanalytics.weebly.com/uploads/1/2/0/4/120443739/ahata-july-2026_orig.png</t>
+          <t>https://tourismanalytics.com/uploads/1/2/0/4/120443739/ahata-august-26_orig.png</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Aruba Hotel Performance YTD 2026 July</t>
+          <t>Aruba Hotel Performance YTD 2026 August</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>2026</v>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>Feb</t>
         </is>
       </c>
       <c r="F11" s="1" t="n">
-        <v>0.8640000000000001</v>
+        <v>0.8959999999999999</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>516.42</v>
+        <v>542.95</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>446.25</v>
+        <v>486.27</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>https://tourismanalytics.weebly.com/uploads/1/2/0/4/120443739/ahata-july-2026_orig.png</t>
+          <t>https://tourismanalytics.com/uploads/1/2/0/4/120443739/ahata-august-26_orig.png</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Aruba Hotel Performance YTD 2026 July</t>
+          <t>Aruba Hotel Performance YTD 2026 August</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>2026</v>
       </c>
       <c r="D12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="F12" s="1" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.8640000000000001</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>454.22</v>
+        <v>516.42</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>366.68</v>
+        <v>446.25</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>https://tourismanalytics.weebly.com/uploads/1/2/0/4/120443739/ahata-july-2026_orig.png</t>
+          <t>https://tourismanalytics.com/uploads/1/2/0/4/120443739/ahata-august-26_orig.png</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Aruba Hotel Performance YTD 2026 July</t>
+          <t>Aruba Hotel Performance YTD 2026 August</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>2026</v>
       </c>
       <c r="D13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>May</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="F13" s="1" t="n">
-        <v>0.7140000000000001</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>421.02</v>
+        <v>454.22</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>300.43</v>
+        <v>366.68</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>https://tourismanalytics.weebly.com/uploads/1/2/0/4/120443739/ahata-july-2026_orig.png</t>
+          <t>https://tourismanalytics.com/uploads/1/2/0/4/120443739/ahata-august-26_orig.png</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Aruba Hotel Performance YTD 2026 July</t>
+          <t>Aruba Hotel Performance YTD 2026 August</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>2026</v>
       </c>
       <c r="D14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Jun</t>
+          <t>May</t>
         </is>
       </c>
       <c r="F14" s="1" t="n">
-        <v>0.708</v>
+        <v>0.7140000000000001</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>400.03</v>
+        <v>421.02</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>283.42</v>
+        <v>300.43</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>https://tourismanalytics.weebly.com/uploads/1/2/0/4/120443739/ahata-july-2026_orig.png</t>
+          <t>https://tourismanalytics.com/uploads/1/2/0/4/120443739/ahata-august-26_orig.png</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Aruba Hotel Performance YTD 2026 July</t>
+          <t>Aruba Hotel Performance YTD 2026 August</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>2026</v>
       </c>
       <c r="D15" t="n">
+        <v>6</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+      <c r="F15" s="1" t="n">
+        <v>0.708</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>400.03</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>283.42</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>https://tourismanalytics.com/uploads/1/2/0/4/120443739/ahata-august-26_orig.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Aruba Hotel Performance YTD 2026 August</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D16" t="n">
         <v>7</v>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>Jul</t>
         </is>
       </c>
-      <c r="F15" s="1" t="n">
+      <c r="F16" s="1" t="n">
         <v>0.7559999999999999</v>
       </c>
-      <c r="G15" s="2" t="n">
+      <c r="G16" s="2" t="n">
         <v>444.82</v>
       </c>
-      <c r="H15" s="2" t="n">
+      <c r="H16" s="2" t="n">
         <v>336.18</v>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>https://tourismanalytics.weebly.com/uploads/1/2/0/4/120443739/ahata-july-2026_orig.png</t>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>https://tourismanalytics.com/uploads/1/2/0/4/120443739/ahata-august-26_orig.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Aruba Hotel Performance YTD 2026 August</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D17" t="n">
+        <v>8</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Aug</t>
+        </is>
+      </c>
+      <c r="F17" s="1" t="n">
+        <v>0.759</v>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>410.97</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>311.84</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>https://tourismanalytics.com/uploads/1/2/0/4/120443739/ahata-august-26_orig.png</t>
         </is>
       </c>
     </row>
@@ -1013,7 +1087,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="39" customWidth="1" min="2" max="2"/>
+    <col width="41" customWidth="1" min="2" max="2"/>
     <col width="6" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="7" customWidth="1" min="5" max="5"/>
@@ -1073,12 +1147,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Aruba Hotel Performance YTD 2026 July</t>
+          <t>Aruba Hotel Performance YTD 2026 August</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -1091,29 +1165,29 @@
         </is>
       </c>
       <c r="F2" s="1" t="n">
-        <v>0.7929999999999999</v>
+        <v>0.7879999999999999</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>474.2</v>
+        <v>465.93</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>375.85</v>
+        <v>367.34</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>https://tourismanalytics.weebly.com/uploads/1/2/0/4/120443739/ahata-july-2026_orig.png</t>
+          <t>https://tourismanalytics.com/uploads/1/2/0/4/120443739/ahata-august-26_orig.png</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Aruba Hotel Performance YTD 2026 July</t>
+          <t>Aruba Hotel Performance YTD 2026 August</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -1126,17 +1200,17 @@
         </is>
       </c>
       <c r="F3" s="1" t="n">
-        <v>0.794</v>
+        <v>0.7859999999999999</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>420.56</v>
+        <v>413.96</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>333.83</v>
+        <v>325.47</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>https://tourismanalytics.weebly.com/uploads/1/2/0/4/120443739/ahata-july-2026_orig.png</t>
+          <t>https://tourismanalytics.com/uploads/1/2/0/4/120443739/ahata-august-26_orig.png</t>
         </is>
       </c>
     </row>

--- a/public/aruba_hotel_history.xlsx
+++ b/public/aruba_hotel_history.xlsx
@@ -483,7 +483,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -520,7 +520,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -557,7 +557,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -594,7 +594,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -631,7 +631,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -668,7 +668,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -705,7 +705,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -742,7 +742,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -779,7 +779,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -816,7 +816,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -853,7 +853,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -890,7 +890,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -927,7 +927,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -964,7 +964,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1001,7 +1001,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1038,7 +1038,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1147,7 +1147,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1182,7 +1182,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">

--- a/public/aruba_hotel_history.xlsx
+++ b/public/aruba_hotel_history.xlsx
@@ -483,7 +483,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -520,7 +520,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -557,7 +557,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -594,7 +594,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -631,7 +631,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -668,7 +668,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -705,7 +705,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -742,7 +742,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -779,7 +779,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -816,7 +816,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -853,7 +853,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -890,7 +890,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -927,7 +927,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -964,7 +964,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1001,7 +1001,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1038,7 +1038,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1147,7 +1147,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1182,7 +1182,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">

--- a/public/aruba_hotel_history.xlsx
+++ b/public/aruba_hotel_history.xlsx
@@ -483,7 +483,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -513,14 +513,14 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>https://tourismanalytics.com/uploads/1/2/0/4/120443739/ahata-august-26_orig.png</t>
+          <t>https://tourismanalytics.weebly.com/uploads/1/2/0/4/120443739/ahata-august-26_orig.png</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -550,14 +550,14 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>https://tourismanalytics.com/uploads/1/2/0/4/120443739/ahata-august-26_orig.png</t>
+          <t>https://tourismanalytics.weebly.com/uploads/1/2/0/4/120443739/ahata-august-26_orig.png</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -587,14 +587,14 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>https://tourismanalytics.com/uploads/1/2/0/4/120443739/ahata-august-26_orig.png</t>
+          <t>https://tourismanalytics.weebly.com/uploads/1/2/0/4/120443739/ahata-august-26_orig.png</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -624,14 +624,14 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>https://tourismanalytics.com/uploads/1/2/0/4/120443739/ahata-august-26_orig.png</t>
+          <t>https://tourismanalytics.weebly.com/uploads/1/2/0/4/120443739/ahata-august-26_orig.png</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -661,14 +661,14 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>https://tourismanalytics.com/uploads/1/2/0/4/120443739/ahata-august-26_orig.png</t>
+          <t>https://tourismanalytics.weebly.com/uploads/1/2/0/4/120443739/ahata-august-26_orig.png</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -698,14 +698,14 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>https://tourismanalytics.com/uploads/1/2/0/4/120443739/ahata-august-26_orig.png</t>
+          <t>https://tourismanalytics.weebly.com/uploads/1/2/0/4/120443739/ahata-august-26_orig.png</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -735,14 +735,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>https://tourismanalytics.com/uploads/1/2/0/4/120443739/ahata-august-26_orig.png</t>
+          <t>https://tourismanalytics.weebly.com/uploads/1/2/0/4/120443739/ahata-august-26_orig.png</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -772,14 +772,14 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>https://tourismanalytics.com/uploads/1/2/0/4/120443739/ahata-august-26_orig.png</t>
+          <t>https://tourismanalytics.weebly.com/uploads/1/2/0/4/120443739/ahata-august-26_orig.png</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -809,14 +809,14 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>https://tourismanalytics.com/uploads/1/2/0/4/120443739/ahata-august-26_orig.png</t>
+          <t>https://tourismanalytics.weebly.com/uploads/1/2/0/4/120443739/ahata-august-26_orig.png</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -846,14 +846,14 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>https://tourismanalytics.com/uploads/1/2/0/4/120443739/ahata-august-26_orig.png</t>
+          <t>https://tourismanalytics.weebly.com/uploads/1/2/0/4/120443739/ahata-august-26_orig.png</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -883,14 +883,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>https://tourismanalytics.com/uploads/1/2/0/4/120443739/ahata-august-26_orig.png</t>
+          <t>https://tourismanalytics.weebly.com/uploads/1/2/0/4/120443739/ahata-august-26_orig.png</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -920,14 +920,14 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>https://tourismanalytics.com/uploads/1/2/0/4/120443739/ahata-august-26_orig.png</t>
+          <t>https://tourismanalytics.weebly.com/uploads/1/2/0/4/120443739/ahata-august-26_orig.png</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -957,14 +957,14 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>https://tourismanalytics.com/uploads/1/2/0/4/120443739/ahata-august-26_orig.png</t>
+          <t>https://tourismanalytics.weebly.com/uploads/1/2/0/4/120443739/ahata-august-26_orig.png</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -994,14 +994,14 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>https://tourismanalytics.com/uploads/1/2/0/4/120443739/ahata-august-26_orig.png</t>
+          <t>https://tourismanalytics.weebly.com/uploads/1/2/0/4/120443739/ahata-august-26_orig.png</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1031,14 +1031,14 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>https://tourismanalytics.com/uploads/1/2/0/4/120443739/ahata-august-26_orig.png</t>
+          <t>https://tourismanalytics.weebly.com/uploads/1/2/0/4/120443739/ahata-august-26_orig.png</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>https://tourismanalytics.com/uploads/1/2/0/4/120443739/ahata-august-26_orig.png</t>
+          <t>https://tourismanalytics.weebly.com/uploads/1/2/0/4/120443739/ahata-august-26_orig.png</t>
         </is>
       </c>
     </row>
@@ -1147,7 +1147,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1175,14 +1175,14 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>https://tourismanalytics.com/uploads/1/2/0/4/120443739/ahata-august-26_orig.png</t>
+          <t>https://tourismanalytics.weebly.com/uploads/1/2/0/4/120443739/ahata-august-26_orig.png</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1210,7 +1210,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>https://tourismanalytics.com/uploads/1/2/0/4/120443739/ahata-august-26_orig.png</t>
+          <t>https://tourismanalytics.weebly.com/uploads/1/2/0/4/120443739/ahata-august-26_orig.png</t>
         </is>
       </c>
     </row>

--- a/public/aruba_hotel_history.xlsx
+++ b/public/aruba_hotel_history.xlsx
@@ -483,7 +483,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -513,14 +513,14 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>https://tourismanalytics.weebly.com/uploads/1/2/0/4/120443739/ahata-august-26_orig.png</t>
+          <t>https://tourismanalytics.com/uploads/1/2/0/4/120443739/ahata-august-26_orig.png</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -550,14 +550,14 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>https://tourismanalytics.weebly.com/uploads/1/2/0/4/120443739/ahata-august-26_orig.png</t>
+          <t>https://tourismanalytics.com/uploads/1/2/0/4/120443739/ahata-august-26_orig.png</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -587,14 +587,14 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>https://tourismanalytics.weebly.com/uploads/1/2/0/4/120443739/ahata-august-26_orig.png</t>
+          <t>https://tourismanalytics.com/uploads/1/2/0/4/120443739/ahata-august-26_orig.png</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -624,14 +624,14 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>https://tourismanalytics.weebly.com/uploads/1/2/0/4/120443739/ahata-august-26_orig.png</t>
+          <t>https://tourismanalytics.com/uploads/1/2/0/4/120443739/ahata-august-26_orig.png</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -661,14 +661,14 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>https://tourismanalytics.weebly.com/uploads/1/2/0/4/120443739/ahata-august-26_orig.png</t>
+          <t>https://tourismanalytics.com/uploads/1/2/0/4/120443739/ahata-august-26_orig.png</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -698,14 +698,14 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>https://tourismanalytics.weebly.com/uploads/1/2/0/4/120443739/ahata-august-26_orig.png</t>
+          <t>https://tourismanalytics.com/uploads/1/2/0/4/120443739/ahata-august-26_orig.png</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -735,14 +735,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>https://tourismanalytics.weebly.com/uploads/1/2/0/4/120443739/ahata-august-26_orig.png</t>
+          <t>https://tourismanalytics.com/uploads/1/2/0/4/120443739/ahata-august-26_orig.png</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -772,14 +772,14 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>https://tourismanalytics.weebly.com/uploads/1/2/0/4/120443739/ahata-august-26_orig.png</t>
+          <t>https://tourismanalytics.com/uploads/1/2/0/4/120443739/ahata-august-26_orig.png</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -809,14 +809,14 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>https://tourismanalytics.weebly.com/uploads/1/2/0/4/120443739/ahata-august-26_orig.png</t>
+          <t>https://tourismanalytics.com/uploads/1/2/0/4/120443739/ahata-august-26_orig.png</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -846,14 +846,14 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>https://tourismanalytics.weebly.com/uploads/1/2/0/4/120443739/ahata-august-26_orig.png</t>
+          <t>https://tourismanalytics.com/uploads/1/2/0/4/120443739/ahata-august-26_orig.png</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -883,14 +883,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>https://tourismanalytics.weebly.com/uploads/1/2/0/4/120443739/ahata-august-26_orig.png</t>
+          <t>https://tourismanalytics.com/uploads/1/2/0/4/120443739/ahata-august-26_orig.png</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -920,14 +920,14 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>https://tourismanalytics.weebly.com/uploads/1/2/0/4/120443739/ahata-august-26_orig.png</t>
+          <t>https://tourismanalytics.com/uploads/1/2/0/4/120443739/ahata-august-26_orig.png</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -957,14 +957,14 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>https://tourismanalytics.weebly.com/uploads/1/2/0/4/120443739/ahata-august-26_orig.png</t>
+          <t>https://tourismanalytics.com/uploads/1/2/0/4/120443739/ahata-august-26_orig.png</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -994,14 +994,14 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>https://tourismanalytics.weebly.com/uploads/1/2/0/4/120443739/ahata-august-26_orig.png</t>
+          <t>https://tourismanalytics.com/uploads/1/2/0/4/120443739/ahata-august-26_orig.png</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1031,14 +1031,14 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>https://tourismanalytics.weebly.com/uploads/1/2/0/4/120443739/ahata-august-26_orig.png</t>
+          <t>https://tourismanalytics.com/uploads/1/2/0/4/120443739/ahata-august-26_orig.png</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>https://tourismanalytics.weebly.com/uploads/1/2/0/4/120443739/ahata-august-26_orig.png</t>
+          <t>https://tourismanalytics.com/uploads/1/2/0/4/120443739/ahata-august-26_orig.png</t>
         </is>
       </c>
     </row>
@@ -1147,7 +1147,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1175,14 +1175,14 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>https://tourismanalytics.weebly.com/uploads/1/2/0/4/120443739/ahata-august-26_orig.png</t>
+          <t>https://tourismanalytics.com/uploads/1/2/0/4/120443739/ahata-august-26_orig.png</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1210,7 +1210,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>https://tourismanalytics.weebly.com/uploads/1/2/0/4/120443739/ahata-august-26_orig.png</t>
+          <t>https://tourismanalytics.com/uploads/1/2/0/4/120443739/ahata-august-26_orig.png</t>
         </is>
       </c>
     </row>

--- a/public/aruba_hotel_history.xlsx
+++ b/public/aruba_hotel_history.xlsx
@@ -419,11 +419,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="41" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
     <col width="6" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="7" customWidth="1" min="5" max="5"/>
@@ -483,12 +483,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Aruba Hotel Performance YTD 2026 August</t>
+          <t>Aruba Hotel Performance YTD 2026 September</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -513,19 +513,19 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>https://tourismanalytics.com/uploads/1/2/0/4/120443739/ahata-august-26_orig.png</t>
+          <t>https://tourismanalytics.com/uploads/1/2/0/4/120443739/aruba-hotel-opy-sep-26_orig.png</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Aruba Hotel Performance YTD 2026 August</t>
+          <t>Aruba Hotel Performance YTD 2026 September</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -550,19 +550,19 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>https://tourismanalytics.com/uploads/1/2/0/4/120443739/ahata-august-26_orig.png</t>
+          <t>https://tourismanalytics.com/uploads/1/2/0/4/120443739/aruba-hotel-opy-sep-26_orig.png</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Aruba Hotel Performance YTD 2026 August</t>
+          <t>Aruba Hotel Performance YTD 2026 September</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -587,19 +587,19 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>https://tourismanalytics.com/uploads/1/2/0/4/120443739/ahata-august-26_orig.png</t>
+          <t>https://tourismanalytics.com/uploads/1/2/0/4/120443739/aruba-hotel-opy-sep-26_orig.png</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Aruba Hotel Performance YTD 2026 August</t>
+          <t>Aruba Hotel Performance YTD 2026 September</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -624,19 +624,19 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>https://tourismanalytics.com/uploads/1/2/0/4/120443739/ahata-august-26_orig.png</t>
+          <t>https://tourismanalytics.com/uploads/1/2/0/4/120443739/aruba-hotel-opy-sep-26_orig.png</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Aruba Hotel Performance YTD 2026 August</t>
+          <t>Aruba Hotel Performance YTD 2026 September</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -661,19 +661,19 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>https://tourismanalytics.com/uploads/1/2/0/4/120443739/ahata-august-26_orig.png</t>
+          <t>https://tourismanalytics.com/uploads/1/2/0/4/120443739/aruba-hotel-opy-sep-26_orig.png</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Aruba Hotel Performance YTD 2026 August</t>
+          <t>Aruba Hotel Performance YTD 2026 September</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -698,19 +698,19 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>https://tourismanalytics.com/uploads/1/2/0/4/120443739/ahata-august-26_orig.png</t>
+          <t>https://tourismanalytics.com/uploads/1/2/0/4/120443739/aruba-hotel-opy-sep-26_orig.png</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Aruba Hotel Performance YTD 2026 August</t>
+          <t>Aruba Hotel Performance YTD 2026 September</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -735,19 +735,19 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>https://tourismanalytics.com/uploads/1/2/0/4/120443739/ahata-august-26_orig.png</t>
+          <t>https://tourismanalytics.com/uploads/1/2/0/4/120443739/aruba-hotel-opy-sep-26_orig.png</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Aruba Hotel Performance YTD 2026 August</t>
+          <t>Aruba Hotel Performance YTD 2026 September</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -772,303 +772,377 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>https://tourismanalytics.com/uploads/1/2/0/4/120443739/ahata-august-26_orig.png</t>
+          <t>https://tourismanalytics.com/uploads/1/2/0/4/120443739/aruba-hotel-opy-sep-26_orig.png</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Aruba Hotel Performance YTD 2026 August</t>
+          <t>Aruba Hotel Performance YTD 2026 September</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Jan</t>
+          <t>Sep</t>
         </is>
       </c>
       <c r="F10" s="1" t="n">
-        <v>0.8140000000000001</v>
+        <v>0.633</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>519.26</v>
+        <v>335.9</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>422.91</v>
+        <v>212.69</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>https://tourismanalytics.com/uploads/1/2/0/4/120443739/ahata-august-26_orig.png</t>
+          <t>https://tourismanalytics.com/uploads/1/2/0/4/120443739/aruba-hotel-opy-sep-26_orig.png</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Aruba Hotel Performance YTD 2026 August</t>
+          <t>Aruba Hotel Performance YTD 2026 September</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>2026</v>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Feb</t>
+          <t>Jan</t>
         </is>
       </c>
       <c r="F11" s="1" t="n">
-        <v>0.8959999999999999</v>
+        <v>0.8140000000000001</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>542.95</v>
+        <v>519.26</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>486.27</v>
+        <v>422.91</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>https://tourismanalytics.com/uploads/1/2/0/4/120443739/ahata-august-26_orig.png</t>
+          <t>https://tourismanalytics.com/uploads/1/2/0/4/120443739/aruba-hotel-opy-sep-26_orig.png</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Aruba Hotel Performance YTD 2026 August</t>
+          <t>Aruba Hotel Performance YTD 2026 September</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>2026</v>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>Feb</t>
         </is>
       </c>
       <c r="F12" s="1" t="n">
-        <v>0.8640000000000001</v>
+        <v>0.8959999999999999</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>516.42</v>
+        <v>542.95</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>446.25</v>
+        <v>486.27</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>https://tourismanalytics.com/uploads/1/2/0/4/120443739/ahata-august-26_orig.png</t>
+          <t>https://tourismanalytics.com/uploads/1/2/0/4/120443739/aruba-hotel-opy-sep-26_orig.png</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Aruba Hotel Performance YTD 2026 August</t>
+          <t>Aruba Hotel Performance YTD 2026 September</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>2026</v>
       </c>
       <c r="D13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="F13" s="1" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.8640000000000001</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>454.22</v>
+        <v>516.42</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>366.68</v>
+        <v>446.25</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>https://tourismanalytics.com/uploads/1/2/0/4/120443739/ahata-august-26_orig.png</t>
+          <t>https://tourismanalytics.com/uploads/1/2/0/4/120443739/aruba-hotel-opy-sep-26_orig.png</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Aruba Hotel Performance YTD 2026 August</t>
+          <t>Aruba Hotel Performance YTD 2026 September</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>2026</v>
       </c>
       <c r="D14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>May</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="F14" s="1" t="n">
-        <v>0.7140000000000001</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>421.02</v>
+        <v>454.22</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>300.43</v>
+        <v>366.68</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>https://tourismanalytics.com/uploads/1/2/0/4/120443739/ahata-august-26_orig.png</t>
+          <t>https://tourismanalytics.com/uploads/1/2/0/4/120443739/aruba-hotel-opy-sep-26_orig.png</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Aruba Hotel Performance YTD 2026 August</t>
+          <t>Aruba Hotel Performance YTD 2026 September</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>2026</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Jun</t>
+          <t>May</t>
         </is>
       </c>
       <c r="F15" s="1" t="n">
-        <v>0.708</v>
+        <v>0.7140000000000001</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>400.03</v>
+        <v>421.02</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>283.42</v>
+        <v>300.43</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>https://tourismanalytics.com/uploads/1/2/0/4/120443739/ahata-august-26_orig.png</t>
+          <t>https://tourismanalytics.com/uploads/1/2/0/4/120443739/aruba-hotel-opy-sep-26_orig.png</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Aruba Hotel Performance YTD 2026 August</t>
+          <t>Aruba Hotel Performance YTD 2026 September</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>2026</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Jul</t>
+          <t>Jun</t>
         </is>
       </c>
       <c r="F16" s="1" t="n">
-        <v>0.7559999999999999</v>
+        <v>0.708</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>444.82</v>
+        <v>400.03</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>336.18</v>
+        <v>283.42</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>https://tourismanalytics.com/uploads/1/2/0/4/120443739/ahata-august-26_orig.png</t>
+          <t>https://tourismanalytics.com/uploads/1/2/0/4/120443739/aruba-hotel-opy-sep-26_orig.png</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Aruba Hotel Performance YTD 2026 August</t>
+          <t>Aruba Hotel Performance YTD 2026 September</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>2026</v>
       </c>
       <c r="D17" t="n">
+        <v>7</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="F17" s="1" t="n">
+        <v>0.7559999999999999</v>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>444.82</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>336.18</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>https://tourismanalytics.com/uploads/1/2/0/4/120443739/aruba-hotel-opy-sep-26_orig.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Aruba Hotel Performance YTD 2026 September</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D18" t="n">
         <v>8</v>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>Aug</t>
         </is>
       </c>
-      <c r="F17" s="1" t="n">
+      <c r="F18" s="1" t="n">
         <v>0.759</v>
       </c>
-      <c r="G17" s="2" t="n">
+      <c r="G18" s="2" t="n">
         <v>410.97</v>
       </c>
-      <c r="H17" s="2" t="n">
+      <c r="H18" s="2" t="n">
         <v>311.84</v>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>https://tourismanalytics.com/uploads/1/2/0/4/120443739/ahata-august-26_orig.png</t>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>https://tourismanalytics.com/uploads/1/2/0/4/120443739/aruba-hotel-opy-sep-26_orig.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Aruba Hotel Performance YTD 2026 September</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D19" t="n">
+        <v>9</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Sep</t>
+        </is>
+      </c>
+      <c r="F19" s="1" t="n">
+        <v>0.7340000000000001</v>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>357.31</v>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>262.43</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>https://tourismanalytics.com/uploads/1/2/0/4/120443739/aruba-hotel-opy-sep-26_orig.png</t>
         </is>
       </c>
     </row>
@@ -1087,11 +1161,11 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="41" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
     <col width="6" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="7" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
     <col width="8" customWidth="1" min="8" max="8"/>
     <col width="60" customWidth="1" min="9" max="9"/>
@@ -1147,12 +1221,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Aruba Hotel Performance YTD 2026 August</t>
+          <t>Aruba Hotel Performance YTD 2026 September</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -1165,29 +1239,29 @@
         </is>
       </c>
       <c r="F2" s="1" t="n">
-        <v>0.7879999999999999</v>
+        <v>0.782</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>465.93</v>
+        <v>454.61</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>367.34</v>
+        <v>355.69</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>https://tourismanalytics.com/uploads/1/2/0/4/120443739/ahata-august-26_orig.png</t>
+          <t>https://tourismanalytics.com/uploads/1/2/0/4/120443739/aruba-hotel-opy-sep-26_orig.png</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Aruba Hotel Performance YTD 2026 August</t>
+          <t>Aruba Hotel Performance YTD 2026 September</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -1200,17 +1274,17 @@
         </is>
       </c>
       <c r="F3" s="1" t="n">
-        <v>0.7859999999999999</v>
+        <v>0.769</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>413.96</v>
+        <v>406.58</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>325.47</v>
+        <v>312.52</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>https://tourismanalytics.com/uploads/1/2/0/4/120443739/ahata-august-26_orig.png</t>
+          <t>https://tourismanalytics.com/uploads/1/2/0/4/120443739/aruba-hotel-opy-sep-26_orig.png</t>
         </is>
       </c>
     </row>
